--- a/experiment/Wavlet_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/Wavlet_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.96</v>
+        <v>23.99</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5665</v>
+        <v>0.5689</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.61</v>
+        <v>28.64</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8089</v>
+        <v>0.8108</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.36</v>
+        <v>26.4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8072</v>
+        <v>0.8094</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.58</v>
+        <v>30.59</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8465</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.18</v>
+        <v>26.22</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7054</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.7</v>
+        <v>33.88</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8925999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.15</v>
+        <v>26.17</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7441</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>23.07</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5885</v>
+        <v>0.5898</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>27.41</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7843</v>
+        <v>0.7853</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.26</v>
+        <v>29.27</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8015</v>
+        <v>0.8025</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.2</v>
+        <v>24.34</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7137</v>
+        <v>0.7232</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.83</v>
+        <v>27.93</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7429</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.98</v>
+        <v>30.01</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8061</v>
+        <v>0.8077</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.3</v>
+        <v>29.34</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8267</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>25.02</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6757</v>
+        <v>0.6771</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.76</v>
+        <v>24.74</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7543</v>
+        <v>0.7551</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.52</v>
+        <v>34.58</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8901</v>
+        <v>0.8908</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.82</v>
+        <v>32.89</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8912</v>
+        <v>0.8922</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.06</v>
+        <v>26.1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7328</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.99</v>
+        <v>26.04</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.04</v>
+        <v>22.13</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6756</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.75</v>
+        <v>23.79</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6223</v>
+        <v>0.6239</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.81</v>
+        <v>24.83</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5704</v>
+        <v>0.5722</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.4</v>
+        <v>26.47</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7832</v>
+        <v>0.7864</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.57</v>
+        <v>27.65</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8178</v>
+        <v>0.8199</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26.89</v>
+        <v>26.92</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8338</v>
+        <v>0.8351</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7313</v>
+        <v>0.7334000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.47</v>
+        <v>29.52</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7967</v>
+        <v>0.7989000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.15</v>
+        <v>32.25</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8962</v>
+        <v>0.8983</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.87</v>
+        <v>19.88</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5028</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.7</v>
+        <v>29.73</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8141</v>
+        <v>0.8155</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>20.92</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4254</v>
+        <v>0.4267</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.14</v>
+        <v>25.16</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6674</v>
+        <v>0.6691</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.37</v>
+        <v>24.43</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7522</v>
+        <v>0.7546</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.57</v>
+        <v>34.75</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8878</v>
+        <v>0.8904</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.9</v>
+        <v>26.96</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7372</v>
+        <v>0.7403999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.07</v>
+        <v>28.14</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7114</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>28.45</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7423</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.44</v>
+        <v>35.58</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9510999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.74</v>
+        <v>26.75</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7405</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.7</v>
+        <v>25.75</v>
       </c>
       <c r="C43" t="n">
-        <v>0.715</v>
+        <v>0.7179</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.64</v>
+        <v>26.72</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7586000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27.72</v>
+        <v>27.83</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8689</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.68</v>
+        <v>24.77</v>
       </c>
       <c r="C46" t="n">
-        <v>0.671</v>
+        <v>0.6798</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.46</v>
+        <v>34.62</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8702</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.69</v>
+        <v>22.73</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6157</v>
+        <v>0.6181</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.91</v>
+        <v>24.95</v>
       </c>
       <c r="C49" t="n">
-        <v>0.629</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26.84</v>
+        <v>27.07</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8647</v>
+        <v>0.8704</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.1</v>
+        <v>32.12</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8383</v>
+        <v>0.8391</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.77</v>
+        <v>24.78</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6136</v>
+        <v>0.6153</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.56</v>
+        <v>22.48</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7017</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.24</v>
+        <v>32.34</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.8421999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.53</v>
+        <v>32.55</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7977</v>
+        <v>0.7991</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.61</v>
+        <v>27.65</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7711</v>
+        <v>0.7726</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.51</v>
+        <v>25.57</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6897</v>
+        <v>0.6931</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>21.43</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4195</v>
+        <v>0.4203</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.42</v>
+        <v>27.44</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7232</v>
+        <v>0.7244</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.97</v>
+        <v>31.98</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7909</v>
+        <v>0.7915</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.16</v>
+        <v>31.18</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7841</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.67</v>
+        <v>31.73</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8123</v>
+        <v>0.8144</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.87</v>
+        <v>28.99</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7915</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         <v>33.54</v>
       </c>
       <c r="C64" t="n">
-        <v>0.95</v>
+        <v>0.9509</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.24</v>
+        <v>24.27</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6672</v>
+        <v>0.6692</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.94</v>
+        <v>25.97</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6173</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.27</v>
+        <v>28.31</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7917</v>
+        <v>0.7935</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.44</v>
+        <v>39.6</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9787</v>
+        <v>0.9797</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20.97</v>
+        <v>20.95</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5704</v>
+        <v>0.5717</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>22.76</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6458</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.71</v>
+        <v>28.76</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8084</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.21</v>
+        <v>30.44</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8103</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.43</v>
+        <v>25.44</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5935</v>
+        <v>0.5947</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.19</v>
+        <v>27.21</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6041</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.25</v>
+        <v>26.29</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6937</v>
+        <v>0.6959</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23.94</v>
+        <v>24.04</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>30.66</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7837</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.65</v>
+        <v>23.66</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4756</v>
+        <v>0.4769</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.76</v>
+        <v>29.78</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8086</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.1</v>
+        <v>32.39</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9459</v>
+        <v>0.9487</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.76</v>
+        <v>29.78</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8177</v>
+        <v>0.8187</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.58</v>
+        <v>35.66</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9374</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.46</v>
+        <v>28.5</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7154</v>
+        <v>0.7171999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.2</v>
+        <v>22.24</v>
       </c>
       <c r="C84" t="n">
-        <v>0.524</v>
+        <v>0.5262</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.03</v>
+        <v>21.07</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6001</v>
+        <v>0.6037</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.51</v>
+        <v>25.54</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7802</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.93</v>
+        <v>25</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5951</v>
+        <v>0.5992</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.34</v>
+        <v>27.35</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6924</v>
+        <v>0.6935</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.54</v>
+        <v>30.64</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8092</v>
+        <v>0.8111</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.19</v>
+        <v>27.22</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5589</v>
+        <v>0.5609</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         <v>25.07</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6435</v>
+        <v>0.6445</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.02</v>
+        <v>29.01</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7105</v>
+        <v>0.7109</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.38</v>
+        <v>26.28</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7427</v>
+        <v>0.7408</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.66</v>
+        <v>30.46</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8752</v>
+        <v>0.8756</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>25.82</v>
+        <v>25.92</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7089</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.09</v>
+        <v>26.19</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7993</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.92</v>
+        <v>21.9</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3159</v>
+        <v>0.3165</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27</v>
+        <v>27.02</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5601</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.15</v>
+        <v>26.23</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7744</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.8</v>
+        <v>26.85</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7291</v>
+        <v>0.7316</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24.94</v>
+        <v>25.01</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7166</v>
+        <v>0.7211</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.43</v>
+        <v>27.48</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7313</v>
+        <v>0.7334000000000001</v>
       </c>
     </row>
   </sheetData>
